--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R366c15999b304ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R5bfac48592de4fa8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,25 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +110,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF64748B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6F8FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -180,7 +217,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,6 +327,36 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -497,6 +564,7 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -512,6 +580,9 @@
       <x:c r="D1" s="11" t="str">
         <x:v>visualSetId</x:v>
       </x:c>
+      <x:c r="E1" s="43" t="str">
+        <x:v>combatProfileId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -526,6 +597,9 @@
       <x:c r="D2" s="14" t="str">
         <x:v>int#ref=TbVisualSet</x:v>
       </x:c>
+      <x:c r="E2" s="45" t="str">
+        <x:v>int?#ref=TbSkillCombat</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="30" t="str">
@@ -534,8 +608,9 @@
       <x:c r="B3" s="16"/>
       <x:c r="C3" s="16"/>
       <x:c r="D3" s="16"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="E3" s="46"/>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -547,6 +622,9 @@
       </x:c>
       <x:c r="D4" s="24" t="str">
         <x:v>技能表现集合ID</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="str">
+        <x:v>战斗机制；空值仅为表现目录</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -560,6 +638,9 @@
       <x:c r="D5" s="35" t="n">
         <x:v>30002</x:v>
       </x:c>
+      <x:c r="E5" s="41" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
@@ -572,6 +653,9 @@
       <x:c r="D6" s="36" t="n">
         <x:v>30003</x:v>
       </x:c>
+      <x:c r="E6" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33"/>
@@ -584,6 +668,7 @@
       <x:c r="D7" s="36" t="n">
         <x:v>30004</x:v>
       </x:c>
+      <x:c r="E7" s="41"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33"/>
@@ -596,6 +681,7 @@
       <x:c r="D8" s="36" t="n">
         <x:v>30005</x:v>
       </x:c>
+      <x:c r="E8" s="41"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33"/>
@@ -608,6 +694,7 @@
       <x:c r="D9" s="36" t="n">
         <x:v>30006</x:v>
       </x:c>
+      <x:c r="E9" s="41"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33"/>
@@ -620,6 +707,7 @@
       <x:c r="D10" s="36" t="n">
         <x:v>30007</x:v>
       </x:c>
+      <x:c r="E10" s="41"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33"/>
@@ -632,6 +720,7 @@
       <x:c r="D11" s="36" t="n">
         <x:v>30008</x:v>
       </x:c>
+      <x:c r="E11" s="41"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33"/>
@@ -644,6 +733,7 @@
       <x:c r="D12" s="36" t="n">
         <x:v>30009</x:v>
       </x:c>
+      <x:c r="E12" s="41"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33"/>
@@ -656,6 +746,7 @@
       <x:c r="D13" s="36" t="n">
         <x:v>30010</x:v>
       </x:c>
+      <x:c r="E13" s="41"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33"/>
@@ -668,6 +759,7 @@
       <x:c r="D14" s="36" t="n">
         <x:v>30011</x:v>
       </x:c>
+      <x:c r="E14" s="41"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33"/>
@@ -680,6 +772,7 @@
       <x:c r="D15" s="36" t="n">
         <x:v>30012</x:v>
       </x:c>
+      <x:c r="E15" s="41"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33"/>
@@ -692,6 +785,7 @@
       <x:c r="D16" s="36" t="n">
         <x:v>30013</x:v>
       </x:c>
+      <x:c r="E16" s="41"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33"/>
@@ -704,6 +798,7 @@
       <x:c r="D17" s="36" t="n">
         <x:v>30014</x:v>
       </x:c>
+      <x:c r="E17" s="41"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33"/>
@@ -716,6 +811,7 @@
       <x:c r="D18" s="36" t="n">
         <x:v>30015</x:v>
       </x:c>
+      <x:c r="E18" s="41"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33"/>
@@ -728,6 +824,7 @@
       <x:c r="D19" s="36" t="n">
         <x:v>30016</x:v>
       </x:c>
+      <x:c r="E19" s="41"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="33"/>
@@ -740,6 +837,7 @@
       <x:c r="D20" s="36" t="n">
         <x:v>30017</x:v>
       </x:c>
+      <x:c r="E20" s="41"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33"/>
@@ -752,6 +850,7 @@
       <x:c r="D21" s="36" t="n">
         <x:v>30018</x:v>
       </x:c>
+      <x:c r="E21" s="41"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="33"/>
@@ -764,6 +863,7 @@
       <x:c r="D22" s="36" t="n">
         <x:v>30019</x:v>
       </x:c>
+      <x:c r="E22" s="41"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="33"/>
@@ -776,6 +876,7 @@
       <x:c r="D23" s="36" t="n">
         <x:v>30020</x:v>
       </x:c>
+      <x:c r="E23" s="41"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="33"/>
@@ -788,6 +889,7 @@
       <x:c r="D24" s="36" t="n">
         <x:v>30021</x:v>
       </x:c>
+      <x:c r="E24" s="41"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="33"/>
@@ -800,6 +902,7 @@
       <x:c r="D25" s="36" t="n">
         <x:v>30022</x:v>
       </x:c>
+      <x:c r="E25" s="41"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="33"/>
@@ -812,6 +915,7 @@
       <x:c r="D26" s="36" t="n">
         <x:v>30023</x:v>
       </x:c>
+      <x:c r="E26" s="41"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="33"/>
@@ -824,6 +928,7 @@
       <x:c r="D27" s="36" t="n">
         <x:v>30024</x:v>
       </x:c>
+      <x:c r="E27" s="41"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="33"/>
@@ -836,6 +941,7 @@
       <x:c r="D28" s="36" t="n">
         <x:v>30025</x:v>
       </x:c>
+      <x:c r="E28" s="41"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="33"/>
@@ -848,6 +954,7 @@
       <x:c r="D29" s="36" t="n">
         <x:v>30026</x:v>
       </x:c>
+      <x:c r="E29" s="41"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="33"/>
@@ -860,6 +967,7 @@
       <x:c r="D30" s="36" t="n">
         <x:v>30027</x:v>
       </x:c>
+      <x:c r="E30" s="41"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="33"/>
@@ -872,6 +980,7 @@
       <x:c r="D31" s="36" t="n">
         <x:v>30028</x:v>
       </x:c>
+      <x:c r="E31" s="41"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="33"/>
@@ -884,6 +993,7 @@
       <x:c r="D32" s="36" t="n">
         <x:v>30029</x:v>
       </x:c>
+      <x:c r="E32" s="41"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="33"/>
@@ -896,6 +1006,7 @@
       <x:c r="D33" s="36" t="n">
         <x:v>30030</x:v>
       </x:c>
+      <x:c r="E33" s="41"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="33"/>
@@ -908,6 +1019,7 @@
       <x:c r="D34" s="36" t="n">
         <x:v>30031</x:v>
       </x:c>
+      <x:c r="E34" s="41"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="33"/>
@@ -920,6 +1032,7 @@
       <x:c r="D35" s="36" t="n">
         <x:v>30032</x:v>
       </x:c>
+      <x:c r="E35" s="41"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="33"/>
@@ -932,6 +1045,7 @@
       <x:c r="D36" s="36" t="n">
         <x:v>30033</x:v>
       </x:c>
+      <x:c r="E36" s="41"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="33"/>
@@ -944,6 +1058,7 @@
       <x:c r="D37" s="36" t="n">
         <x:v>30034</x:v>
       </x:c>
+      <x:c r="E37" s="41"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="33"/>
@@ -956,6 +1071,7 @@
       <x:c r="D38" s="36" t="n">
         <x:v>30035</x:v>
       </x:c>
+      <x:c r="E38" s="41"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="33"/>
@@ -968,6 +1084,7 @@
       <x:c r="D39" s="36" t="n">
         <x:v>30036</x:v>
       </x:c>
+      <x:c r="E39" s="41"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="33"/>
@@ -980,6 +1097,7 @@
       <x:c r="D40" s="36" t="n">
         <x:v>30037</x:v>
       </x:c>
+      <x:c r="E40" s="41"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="33"/>
@@ -992,6 +1110,7 @@
       <x:c r="D41" s="36" t="n">
         <x:v>30038</x:v>
       </x:c>
+      <x:c r="E41" s="41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="33"/>
@@ -1004,6 +1123,7 @@
       <x:c r="D42" s="36" t="n">
         <x:v>30039</x:v>
       </x:c>
+      <x:c r="E42" s="41"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="33"/>
@@ -1016,6 +1136,7 @@
       <x:c r="D43" s="36" t="n">
         <x:v>30040</x:v>
       </x:c>
+      <x:c r="E43" s="41"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="33"/>
@@ -1028,6 +1149,7 @@
       <x:c r="D44" s="36" t="n">
         <x:v>30041</x:v>
       </x:c>
+      <x:c r="E44" s="41"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="33"/>
@@ -1040,6 +1162,7 @@
       <x:c r="D45" s="36" t="n">
         <x:v>30042</x:v>
       </x:c>
+      <x:c r="E45" s="41"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="33"/>
@@ -1052,6 +1175,7 @@
       <x:c r="D46" s="36" t="n">
         <x:v>30043</x:v>
       </x:c>
+      <x:c r="E46" s="41"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="33"/>
@@ -1064,6 +1188,7 @@
       <x:c r="D47" s="36" t="n">
         <x:v>30044</x:v>
       </x:c>
+      <x:c r="E47" s="41"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="33"/>
@@ -1076,6 +1201,7 @@
       <x:c r="D48" s="36" t="n">
         <x:v>30045</x:v>
       </x:c>
+      <x:c r="E48" s="41"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="33"/>
@@ -1088,6 +1214,7 @@
       <x:c r="D49" s="36" t="n">
         <x:v>30046</x:v>
       </x:c>
+      <x:c r="E49" s="41"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="33"/>
@@ -1100,6 +1227,7 @@
       <x:c r="D50" s="36" t="n">
         <x:v>30047</x:v>
       </x:c>
+      <x:c r="E50" s="41"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="33"/>
@@ -1112,6 +1240,7 @@
       <x:c r="D51" s="36" t="n">
         <x:v>30048</x:v>
       </x:c>
+      <x:c r="E51" s="41"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="33"/>
@@ -1124,6 +1253,7 @@
       <x:c r="D52" s="36" t="n">
         <x:v>30049</x:v>
       </x:c>
+      <x:c r="E52" s="41"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="33"/>
@@ -1136,6 +1266,7 @@
       <x:c r="D53" s="36" t="n">
         <x:v>30050</x:v>
       </x:c>
+      <x:c r="E53" s="41"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="33"/>
@@ -1148,6 +1279,7 @@
       <x:c r="D54" s="36" t="n">
         <x:v>30051</x:v>
       </x:c>
+      <x:c r="E54" s="41"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="33"/>
@@ -1160,6 +1292,7 @@
       <x:c r="D55" s="36" t="n">
         <x:v>30052</x:v>
       </x:c>
+      <x:c r="E55" s="41"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="33"/>
@@ -1172,6 +1305,7 @@
       <x:c r="D56" s="36" t="n">
         <x:v>30053</x:v>
       </x:c>
+      <x:c r="E56" s="41"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="33"/>
@@ -1184,6 +1318,7 @@
       <x:c r="D57" s="36" t="n">
         <x:v>30054</x:v>
       </x:c>
+      <x:c r="E57" s="41"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="33"/>
@@ -1196,6 +1331,7 @@
       <x:c r="D58" s="36" t="n">
         <x:v>30055</x:v>
       </x:c>
+      <x:c r="E58" s="41"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="33"/>
@@ -1208,6 +1344,7 @@
       <x:c r="D59" s="36" t="n">
         <x:v>30056</x:v>
       </x:c>
+      <x:c r="E59" s="41"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="33"/>
@@ -1220,6 +1357,7 @@
       <x:c r="D60" s="36" t="n">
         <x:v>30057</x:v>
       </x:c>
+      <x:c r="E60" s="41"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="33"/>
@@ -1232,6 +1370,7 @@
       <x:c r="D61" s="36" t="n">
         <x:v>30058</x:v>
       </x:c>
+      <x:c r="E61" s="41"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="33"/>
@@ -1244,6 +1383,7 @@
       <x:c r="D62" s="36" t="n">
         <x:v>30059</x:v>
       </x:c>
+      <x:c r="E62" s="41"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="33"/>
@@ -1256,6 +1396,7 @@
       <x:c r="D63" s="36" t="n">
         <x:v>30060</x:v>
       </x:c>
+      <x:c r="E63" s="41"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="33"/>
@@ -1268,6 +1409,7 @@
       <x:c r="D64" s="36" t="n">
         <x:v>30061</x:v>
       </x:c>
+      <x:c r="E64" s="41"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="33"/>
@@ -1280,6 +1422,7 @@
       <x:c r="D65" s="36" t="n">
         <x:v>30062</x:v>
       </x:c>
+      <x:c r="E65" s="41"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="33"/>
@@ -1292,6 +1435,7 @@
       <x:c r="D66" s="36" t="n">
         <x:v>30063</x:v>
       </x:c>
+      <x:c r="E66" s="41"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="33"/>
@@ -1304,6 +1448,7 @@
       <x:c r="D67" s="36" t="n">
         <x:v>30064</x:v>
       </x:c>
+      <x:c r="E67" s="41"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="33"/>
@@ -1316,6 +1461,7 @@
       <x:c r="D68" s="36" t="n">
         <x:v>30065</x:v>
       </x:c>
+      <x:c r="E68" s="41"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="33"/>
@@ -1328,6 +1474,7 @@
       <x:c r="D69" s="36" t="n">
         <x:v>30066</x:v>
       </x:c>
+      <x:c r="E69" s="41"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="33"/>
@@ -1340,6 +1487,7 @@
       <x:c r="D70" s="36" t="n">
         <x:v>30067</x:v>
       </x:c>
+      <x:c r="E70" s="41"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="33"/>
@@ -1352,6 +1500,7 @@
       <x:c r="D71" s="36" t="n">
         <x:v>30068</x:v>
       </x:c>
+      <x:c r="E71" s="41"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="33"/>
@@ -1364,6 +1513,7 @@
       <x:c r="D72" s="36" t="n">
         <x:v>30069</x:v>
       </x:c>
+      <x:c r="E72" s="41"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="33"/>
@@ -1376,6 +1526,7 @@
       <x:c r="D73" s="36" t="n">
         <x:v>30070</x:v>
       </x:c>
+      <x:c r="E73" s="41"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="33"/>
@@ -1388,6 +1539,7 @@
       <x:c r="D74" s="36" t="n">
         <x:v>30071</x:v>
       </x:c>
+      <x:c r="E74" s="41"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="33"/>
@@ -1400,6 +1552,7 @@
       <x:c r="D75" s="36" t="n">
         <x:v>30072</x:v>
       </x:c>
+      <x:c r="E75" s="41"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="33"/>
@@ -1412,6 +1565,7 @@
       <x:c r="D76" s="36" t="n">
         <x:v>30073</x:v>
       </x:c>
+      <x:c r="E76" s="41"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="33"/>
@@ -1424,6 +1578,7 @@
       <x:c r="D77" s="36" t="n">
         <x:v>30074</x:v>
       </x:c>
+      <x:c r="E77" s="41"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="33"/>
@@ -1436,6 +1591,7 @@
       <x:c r="D78" s="36" t="n">
         <x:v>30075</x:v>
       </x:c>
+      <x:c r="E78" s="41"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="33"/>
@@ -1448,6 +1604,7 @@
       <x:c r="D79" s="36" t="n">
         <x:v>30076</x:v>
       </x:c>
+      <x:c r="E79" s="41"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="33"/>
@@ -1460,6 +1617,7 @@
       <x:c r="D80" s="36" t="n">
         <x:v>30077</x:v>
       </x:c>
+      <x:c r="E80" s="41"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="33"/>
@@ -1472,6 +1630,7 @@
       <x:c r="D81" s="36" t="n">
         <x:v>30078</x:v>
       </x:c>
+      <x:c r="E81" s="41"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="33"/>
@@ -1484,6 +1643,7 @@
       <x:c r="D82" s="36" t="n">
         <x:v>30079</x:v>
       </x:c>
+      <x:c r="E82" s="41"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="33"/>
@@ -1496,6 +1656,7 @@
       <x:c r="D83" s="36" t="n">
         <x:v>30080</x:v>
       </x:c>
+      <x:c r="E83" s="41"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="33"/>
@@ -1508,6 +1669,7 @@
       <x:c r="D84" s="36" t="n">
         <x:v>30081</x:v>
       </x:c>
+      <x:c r="E84" s="41"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="33"/>
@@ -1520,6 +1682,7 @@
       <x:c r="D85" s="36" t="n">
         <x:v>30082</x:v>
       </x:c>
+      <x:c r="E85" s="41"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="33"/>
@@ -1532,6 +1695,7 @@
       <x:c r="D86" s="36" t="n">
         <x:v>30083</x:v>
       </x:c>
+      <x:c r="E86" s="41"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="33"/>
@@ -1544,6 +1708,7 @@
       <x:c r="D87" s="36" t="n">
         <x:v>30084</x:v>
       </x:c>
+      <x:c r="E87" s="41"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="33"/>
@@ -1556,6 +1721,7 @@
       <x:c r="D88" s="36" t="n">
         <x:v>30085</x:v>
       </x:c>
+      <x:c r="E88" s="41"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="33"/>
@@ -1568,6 +1734,7 @@
       <x:c r="D89" s="36" t="n">
         <x:v>30086</x:v>
       </x:c>
+      <x:c r="E89" s="41"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="33"/>
@@ -1580,6 +1747,7 @@
       <x:c r="D90" s="36" t="n">
         <x:v>30087</x:v>
       </x:c>
+      <x:c r="E90" s="41"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="33"/>
@@ -1592,6 +1760,7 @@
       <x:c r="D91" s="36" t="n">
         <x:v>30088</x:v>
       </x:c>
+      <x:c r="E91" s="41"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="33"/>
@@ -1604,6 +1773,7 @@
       <x:c r="D92" s="36" t="n">
         <x:v>30089</x:v>
       </x:c>
+      <x:c r="E92" s="41"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="33"/>
@@ -1616,6 +1786,7 @@
       <x:c r="D93" s="36" t="n">
         <x:v>30090</x:v>
       </x:c>
+      <x:c r="E93" s="41"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="33"/>
@@ -1628,6 +1799,7 @@
       <x:c r="D94" s="36" t="n">
         <x:v>30091</x:v>
       </x:c>
+      <x:c r="E94" s="41"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="33"/>
@@ -1640,6 +1812,7 @@
       <x:c r="D95" s="36" t="n">
         <x:v>30092</x:v>
       </x:c>
+      <x:c r="E95" s="41"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="33"/>
@@ -1652,6 +1825,7 @@
       <x:c r="D96" s="36" t="n">
         <x:v>30093</x:v>
       </x:c>
+      <x:c r="E96" s="41"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="34"/>
@@ -1664,6 +1838,7 @@
       <x:c r="D97" s="37" t="n">
         <x:v>30094</x:v>
       </x:c>
+      <x:c r="E97" s="41"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -1572,13 +1572,13 @@
       <x:c r="E5" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="40" t="n">
+      <x:c r="F5" s="40">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="G5" s="40" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="40" t="n">
+      <x:c r="G5" s="40">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="H5" s="40">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="40" t="n">
@@ -1806,13 +1806,13 @@
       <x:c r="E16" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" s="40" t="n">
+      <x:c r="F16" s="40">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="G16" s="40" t="n">
+      <x:c r="G16" s="40">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="40" t="n">
+      <x:c r="H16" s="40">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="40" t="n">
@@ -2184,13 +2184,13 @@
       <x:c r="E34" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F34" s="40" t="n">
+      <x:c r="F34" s="40">
         <x:v>1225</x:v>
       </x:c>
-      <x:c r="G34" s="40" t="n">
+      <x:c r="G34" s="40">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="40" t="n">
+      <x:c r="H34" s="40">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="40" t="n">

--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R7ac700efaf6744a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="Rb2629634b2cf48d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1445,13 +1445,13 @@
         <x:v>combatProfileId</x:v>
       </x:c>
       <x:c r="F1" s="50" t="str">
-        <x:v>projectileRadiusMilli</x:v>
+        <x:v>projectileRadiusPixelsMilli</x:v>
       </x:c>
       <x:c r="G1" s="50" t="str">
-        <x:v>projectileOffsetXMilli</x:v>
+        <x:v>projectileOffsetXPixelsMilli</x:v>
       </x:c>
       <x:c r="H1" s="50" t="str">
-        <x:v>projectileOffsetYMilli</x:v>
+        <x:v>projectileOffsetYPixelsMilli</x:v>
       </x:c>
       <x:c r="I1" s="50" t="str">
         <x:v>projectileClipId</x:v>
@@ -1463,7 +1463,34 @@
         <x:v>areaClipIds</x:v>
       </x:c>
       <x:c r="L1" s="50" t="str">
-        <x:v>areaRadiusMilli</x:v>
+        <x:v>areaRadiusPixelsMilli</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>projectileVisualOffsetXPixelsMilli</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>projectileVisualOffsetYPixelsMilli</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>projectileVisualScalePermille</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>impactVisualOffsetXPixelsMilli</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>impactVisualOffsetYPixelsMilli</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>impactVisualScalePermille</x:v>
+      </x:c>
+      <x:c r="S1" t="str">
+        <x:v>areaVisualOffsetXPixelsMilli</x:v>
+      </x:c>
+      <x:c r="T1" t="str">
+        <x:v>areaVisualOffsetYPixelsMilli</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>areaVisualScalePermille</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
@@ -1501,6 +1528,33 @@
         <x:v>(list#sep=;),int#ref=TbAnimationClip</x:v>
       </x:c>
       <x:c r="L2" s="53" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
         <x:v>int?</x:v>
       </x:c>
     </x:row>
@@ -1519,6 +1573,15 @@
       <x:c r="J3" s="58"/>
       <x:c r="K3" s="58"/>
       <x:c r="L3" s="58"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="61" t="str">
@@ -1537,13 +1600,13 @@
         <x:v>战斗机制；空值仅为表现目录</x:v>
       </x:c>
       <x:c r="F4" s="62" t="str">
-        <x:v>弹丸半径；世界单位×1000；实际值=表值/1000；最多3位小数；非弹丸留空</x:v>
+        <x:v>弹丸命中半径（像素）；由技能预制体“弹丸命中范围”节点导出；非弹丸留空。</x:v>
       </x:c>
       <x:c r="G4" s="62" t="str">
-        <x:v>碰撞中心横向偏移；技能局部右向；世界单位×1000；实际值=表值/1000；最多3位小数</x:v>
+        <x:v>弹丸命中中心横向偏移（像素）；技能局部右向；由技能预制体导出。</x:v>
       </x:c>
       <x:c r="H4" s="62" t="str">
-        <x:v>碰撞中心纵向偏移；技能局部前向；世界单位×1000；实际值=表值/1000；最多3位小数</x:v>
+        <x:v>弹丸命中中心前向偏移（像素）；由技能预制体导出。</x:v>
       </x:c>
       <x:c r="I4" s="62" t="str">
         <x:v>弹丸飞行表现；Projectile必填</x:v>
@@ -1555,7 +1618,34 @@
         <x:v>TargetArea在目标位置叠加播放的片段</x:v>
       </x:c>
       <x:c r="L4" s="62" t="str">
-        <x:v>TargetArea群体半径，世界单位乘1000</x:v>
+        <x:v>范围技能命中半径（像素）；由技能预制体“范围技能命中范围”节点导出；非范围技能留空。</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>弹丸表现横向偏移（逻辑像素）；由技能预制体“弹丸表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>弹丸表现纵向偏移（逻辑像素）；由技能预制体“弹丸表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>弹丸表现相对缩放（千分比）；由技能预制体“弹丸表现”节点统一 Scale 导出。</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>命中特效表现横向偏移（逻辑像素）；由技能预制体“命中特效表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>命中特效表现纵向偏移（逻辑像素）；由技能预制体“命中特效表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v>命中特效表现相对缩放（千分比）；由技能预制体“命中特效表现”节点统一 Scale 导出。</x:v>
+      </x:c>
+      <x:c r="S4" t="str">
+        <x:v>范围特效表现横向偏移（逻辑像素）；由技能预制体“范围特效表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="T4" t="str">
+        <x:v>范围特效表现纵向偏移（逻辑像素）；由技能预制体“范围特效表现”节点导出。</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>范围特效表现相对缩放（千分比）；由技能预制体“范围特效表现”节点统一 Scale 导出。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="14.5">
@@ -1573,13 +1663,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="40">
-        <x:v>700</x:v>
+        <x:v>30693</x:v>
       </x:c>
       <x:c r="G5" s="40">
-        <x:v>1140</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="H5" s="40">
-        <x:v>0</x:v>
+        <x:v>-25000</x:v>
       </x:c>
       <x:c r="I5" s="40" t="n">
         <x:v>30002</x:v>
@@ -1589,6 +1679,24 @@
       </x:c>
       <x:c r="K5" s="40"/>
       <x:c r="L5" s="40"/>
+      <x:c r="M5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="14.5">
       <x:c r="A6" s="40"/>
@@ -1611,6 +1719,15 @@
       <x:c r="J6" s="40"/>
       <x:c r="K6" s="40"/>
       <x:c r="L6" s="40"/>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
+      <x:c r="Q6"/>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
     </x:row>
     <x:row r="7" ht="14.5">
       <x:c r="A7" s="40"/>
@@ -1631,6 +1748,15 @@
       <x:c r="J7" s="40"/>
       <x:c r="K7" s="40"/>
       <x:c r="L7" s="40"/>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
+      <x:c r="Q7"/>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
     </x:row>
     <x:row r="8" ht="14.5">
       <x:c r="A8" s="40"/>
@@ -1651,6 +1777,15 @@
       <x:c r="J8" s="40"/>
       <x:c r="K8" s="40"/>
       <x:c r="L8" s="40"/>
+      <x:c r="M8"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8"/>
+      <x:c r="Q8"/>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
     </x:row>
     <x:row r="9" ht="14.5">
       <x:c r="A9" s="40"/>
@@ -1671,6 +1806,15 @@
       <x:c r="J9" s="40"/>
       <x:c r="K9" s="40"/>
       <x:c r="L9" s="40"/>
+      <x:c r="M9"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
+      <x:c r="Q9"/>
+      <x:c r="R9"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
     </x:row>
     <x:row r="10" ht="14.5">
       <x:c r="A10" s="40"/>
@@ -1691,6 +1835,15 @@
       <x:c r="J10" s="40"/>
       <x:c r="K10" s="40"/>
       <x:c r="L10" s="40"/>
+      <x:c r="M10"/>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+      <x:c r="P10"/>
+      <x:c r="Q10"/>
+      <x:c r="R10"/>
+      <x:c r="S10"/>
+      <x:c r="T10"/>
+      <x:c r="U10"/>
     </x:row>
     <x:row r="11" ht="14.5">
       <x:c r="A11" s="40"/>
@@ -1711,6 +1864,15 @@
       <x:c r="J11" s="40"/>
       <x:c r="K11" s="40"/>
       <x:c r="L11" s="40"/>
+      <x:c r="M11"/>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+      <x:c r="P11"/>
+      <x:c r="Q11"/>
+      <x:c r="R11"/>
+      <x:c r="S11"/>
+      <x:c r="T11"/>
+      <x:c r="U11"/>
     </x:row>
     <x:row r="12" ht="14.5">
       <x:c r="A12" s="40"/>
@@ -1731,6 +1893,15 @@
       <x:c r="J12" s="40"/>
       <x:c r="K12" s="40"/>
       <x:c r="L12" s="40"/>
+      <x:c r="M12"/>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+      <x:c r="P12"/>
+      <x:c r="Q12"/>
+      <x:c r="R12"/>
+      <x:c r="S12"/>
+      <x:c r="T12"/>
+      <x:c r="U12"/>
     </x:row>
     <x:row r="13" ht="14.5">
       <x:c r="A13" s="40"/>
@@ -1751,6 +1922,15 @@
       <x:c r="J13" s="40"/>
       <x:c r="K13" s="40"/>
       <x:c r="L13" s="40"/>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
+      <x:c r="Q13"/>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
+      <x:c r="T13"/>
+      <x:c r="U13"/>
     </x:row>
     <x:row r="14" ht="14.5">
       <x:c r="A14" s="40"/>
@@ -1771,6 +1951,15 @@
       <x:c r="J14" s="40"/>
       <x:c r="K14" s="40"/>
       <x:c r="L14" s="40"/>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+      <x:c r="Q14"/>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
     </x:row>
     <x:row r="15" ht="14.5">
       <x:c r="A15" s="40"/>
@@ -1791,6 +1980,15 @@
       <x:c r="J15" s="40"/>
       <x:c r="K15" s="40"/>
       <x:c r="L15" s="40"/>
+      <x:c r="M15"/>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15"/>
+      <x:c r="Q15"/>
+      <x:c r="R15"/>
+      <x:c r="S15"/>
+      <x:c r="T15"/>
+      <x:c r="U15"/>
     </x:row>
     <x:row r="16" ht="14.5">
       <x:c r="A16" s="40"/>
@@ -1807,7 +2005,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="40">
-        <x:v>630</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G16" s="40">
         <x:v>0</x:v>
@@ -1823,6 +2021,24 @@
       </x:c>
       <x:c r="K16" s="40"/>
       <x:c r="L16" s="40"/>
+      <x:c r="M16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="14.5">
       <x:c r="A17" s="40"/>
@@ -1843,6 +2059,15 @@
       <x:c r="J17" s="40"/>
       <x:c r="K17" s="40"/>
       <x:c r="L17" s="40"/>
+      <x:c r="M17"/>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
+      <x:c r="Q17"/>
+      <x:c r="R17"/>
+      <x:c r="S17"/>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
     </x:row>
     <x:row r="18" ht="14.5">
       <x:c r="A18" s="40"/>
@@ -1863,6 +2088,15 @@
       <x:c r="J18" s="40"/>
       <x:c r="K18" s="40"/>
       <x:c r="L18" s="40"/>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
+      <x:c r="Q18"/>
+      <x:c r="R18"/>
+      <x:c r="S18"/>
+      <x:c r="T18"/>
+      <x:c r="U18"/>
     </x:row>
     <x:row r="19" ht="14.5">
       <x:c r="A19" s="40"/>
@@ -1883,6 +2117,15 @@
       <x:c r="J19" s="40"/>
       <x:c r="K19" s="40"/>
       <x:c r="L19" s="40"/>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
+      <x:c r="Q19"/>
+      <x:c r="R19"/>
+      <x:c r="S19"/>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
     </x:row>
     <x:row r="20" ht="14.5">
       <x:c r="A20" s="40"/>
@@ -1903,6 +2146,15 @@
       <x:c r="J20" s="40"/>
       <x:c r="K20" s="40"/>
       <x:c r="L20" s="40"/>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
+      <x:c r="Q20"/>
+      <x:c r="R20"/>
+      <x:c r="S20"/>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
     </x:row>
     <x:row r="21" ht="14.5">
       <x:c r="A21" s="40"/>
@@ -1923,6 +2175,15 @@
       <x:c r="J21" s="40"/>
       <x:c r="K21" s="40"/>
       <x:c r="L21" s="40"/>
+      <x:c r="M21"/>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
+      <x:c r="Q21"/>
+      <x:c r="R21"/>
+      <x:c r="S21"/>
+      <x:c r="T21"/>
+      <x:c r="U21"/>
     </x:row>
     <x:row r="22" ht="14.5">
       <x:c r="A22" s="40"/>
@@ -1943,6 +2204,15 @@
       <x:c r="J22" s="40"/>
       <x:c r="K22" s="40"/>
       <x:c r="L22" s="40"/>
+      <x:c r="M22"/>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
+      <x:c r="Q22"/>
+      <x:c r="R22"/>
+      <x:c r="S22"/>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
     </x:row>
     <x:row r="23" ht="14.5">
       <x:c r="A23" s="40"/>
@@ -1963,6 +2233,15 @@
       <x:c r="J23" s="40"/>
       <x:c r="K23" s="40"/>
       <x:c r="L23" s="40"/>
+      <x:c r="M23"/>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
+      <x:c r="Q23"/>
+      <x:c r="R23"/>
+      <x:c r="S23"/>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
     </x:row>
     <x:row r="24" ht="14.5">
       <x:c r="A24" s="40"/>
@@ -1983,6 +2262,15 @@
       <x:c r="J24" s="40"/>
       <x:c r="K24" s="40"/>
       <x:c r="L24" s="40"/>
+      <x:c r="M24"/>
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
+      <x:c r="Q24"/>
+      <x:c r="R24"/>
+      <x:c r="S24"/>
+      <x:c r="T24"/>
+      <x:c r="U24"/>
     </x:row>
     <x:row r="25" ht="14.5">
       <x:c r="A25" s="40"/>
@@ -2003,6 +2291,15 @@
       <x:c r="J25" s="40"/>
       <x:c r="K25" s="40"/>
       <x:c r="L25" s="40"/>
+      <x:c r="M25"/>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
+      <x:c r="Q25"/>
+      <x:c r="R25"/>
+      <x:c r="S25"/>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
     </x:row>
     <x:row r="26" ht="14.5">
       <x:c r="A26" s="40"/>
@@ -2023,6 +2320,15 @@
       <x:c r="J26" s="40"/>
       <x:c r="K26" s="40"/>
       <x:c r="L26" s="40"/>
+      <x:c r="M26"/>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
+      <x:c r="Q26"/>
+      <x:c r="R26"/>
+      <x:c r="S26"/>
+      <x:c r="T26"/>
+      <x:c r="U26"/>
     </x:row>
     <x:row r="27" ht="14.5">
       <x:c r="A27" s="40"/>
@@ -2043,6 +2349,15 @@
       <x:c r="J27" s="40"/>
       <x:c r="K27" s="40"/>
       <x:c r="L27" s="40"/>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+      <x:c r="Q27"/>
+      <x:c r="R27"/>
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
     </x:row>
     <x:row r="28" ht="14.5">
       <x:c r="A28" s="40"/>
@@ -2063,6 +2378,15 @@
       <x:c r="J28" s="40"/>
       <x:c r="K28" s="40"/>
       <x:c r="L28" s="40"/>
+      <x:c r="M28"/>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
+      <x:c r="R28"/>
+      <x:c r="S28"/>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
     </x:row>
     <x:row r="29" ht="14.5">
       <x:c r="A29" s="40"/>
@@ -2083,6 +2407,15 @@
       <x:c r="J29" s="40"/>
       <x:c r="K29" s="40"/>
       <x:c r="L29" s="40"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
+      <x:c r="Q29"/>
+      <x:c r="R29"/>
+      <x:c r="S29"/>
+      <x:c r="T29"/>
+      <x:c r="U29"/>
     </x:row>
     <x:row r="30" ht="14.5">
       <x:c r="A30" s="40"/>
@@ -2106,8 +2439,17 @@
       <x:c r="K30" s="40" t="str">
         <x:v>30045</x:v>
       </x:c>
-      <x:c r="L30" s="40" t="n">
-        <x:v>1065</x:v>
+      <x:c r="L30" s="40">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="S30">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T30">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U30">
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="14.5">
@@ -2129,6 +2471,15 @@
       <x:c r="J31" s="40"/>
       <x:c r="K31" s="40"/>
       <x:c r="L31" s="40"/>
+      <x:c r="M31"/>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
+      <x:c r="Q31"/>
+      <x:c r="R31"/>
+      <x:c r="S31"/>
+      <x:c r="T31"/>
+      <x:c r="U31"/>
     </x:row>
     <x:row r="32" ht="14.5">
       <x:c r="A32" s="40"/>
@@ -2149,6 +2500,15 @@
       <x:c r="J32" s="40"/>
       <x:c r="K32" s="40"/>
       <x:c r="L32" s="40"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
+      <x:c r="Q32"/>
+      <x:c r="R32"/>
+      <x:c r="S32"/>
+      <x:c r="T32"/>
+      <x:c r="U32"/>
     </x:row>
     <x:row r="33" ht="14.5">
       <x:c r="A33" s="40"/>
@@ -2169,6 +2529,15 @@
       <x:c r="J33" s="40"/>
       <x:c r="K33" s="40"/>
       <x:c r="L33" s="40"/>
+      <x:c r="M33"/>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
+      <x:c r="S33"/>
+      <x:c r="T33"/>
+      <x:c r="U33"/>
     </x:row>
     <x:row r="34" ht="14.5">
       <x:c r="A34" s="40"/>
@@ -2185,7 +2554,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F34" s="40">
-        <x:v>1225</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G34" s="40">
         <x:v>0</x:v>
@@ -2201,6 +2570,24 @@
       </x:c>
       <x:c r="K34" s="40"/>
       <x:c r="L34" s="40"/>
+      <x:c r="M34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R34">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="14.5">
       <x:c r="A35" s="40"/>
@@ -2221,6 +2608,15 @@
       <x:c r="J35" s="40"/>
       <x:c r="K35" s="40"/>
       <x:c r="L35" s="40"/>
+      <x:c r="M35"/>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
     </x:row>
     <x:row r="36" ht="14.5">
       <x:c r="A36" s="40"/>
@@ -2241,6 +2637,15 @@
       <x:c r="J36" s="40"/>
       <x:c r="K36" s="40"/>
       <x:c r="L36" s="40"/>
+      <x:c r="M36"/>
+      <x:c r="N36"/>
+      <x:c r="O36"/>
+      <x:c r="P36"/>
+      <x:c r="Q36"/>
+      <x:c r="R36"/>
+      <x:c r="S36"/>
+      <x:c r="T36"/>
+      <x:c r="U36"/>
     </x:row>
     <x:row r="37" ht="14.5">
       <x:c r="A37" s="40"/>
@@ -2261,6 +2666,15 @@
       <x:c r="J37" s="40"/>
       <x:c r="K37" s="40"/>
       <x:c r="L37" s="40"/>
+      <x:c r="M37"/>
+      <x:c r="N37"/>
+      <x:c r="O37"/>
+      <x:c r="P37"/>
+      <x:c r="Q37"/>
+      <x:c r="R37"/>
+      <x:c r="S37"/>
+      <x:c r="T37"/>
+      <x:c r="U37"/>
     </x:row>
     <x:row r="38" ht="14.5">
       <x:c r="A38" s="40"/>
@@ -2281,6 +2695,15 @@
       <x:c r="J38" s="40"/>
       <x:c r="K38" s="40"/>
       <x:c r="L38" s="40"/>
+      <x:c r="M38"/>
+      <x:c r="N38"/>
+      <x:c r="O38"/>
+      <x:c r="P38"/>
+      <x:c r="Q38"/>
+      <x:c r="R38"/>
+      <x:c r="S38"/>
+      <x:c r="T38"/>
+      <x:c r="U38"/>
     </x:row>
     <x:row r="39" ht="14.5">
       <x:c r="A39" s="40"/>
@@ -2301,6 +2724,15 @@
       <x:c r="J39" s="40"/>
       <x:c r="K39" s="40"/>
       <x:c r="L39" s="40"/>
+      <x:c r="M39"/>
+      <x:c r="N39"/>
+      <x:c r="O39"/>
+      <x:c r="P39"/>
+      <x:c r="Q39"/>
+      <x:c r="R39"/>
+      <x:c r="S39"/>
+      <x:c r="T39"/>
+      <x:c r="U39"/>
     </x:row>
     <x:row r="40" ht="14.5">
       <x:c r="A40" s="40"/>
@@ -2321,6 +2753,15 @@
       <x:c r="J40" s="40"/>
       <x:c r="K40" s="40"/>
       <x:c r="L40" s="40"/>
+      <x:c r="M40"/>
+      <x:c r="N40"/>
+      <x:c r="O40"/>
+      <x:c r="P40"/>
+      <x:c r="Q40"/>
+      <x:c r="R40"/>
+      <x:c r="S40"/>
+      <x:c r="T40"/>
+      <x:c r="U40"/>
     </x:row>
     <x:row r="41" ht="14.5">
       <x:c r="A41" s="40"/>
@@ -2341,6 +2782,15 @@
       <x:c r="J41" s="40"/>
       <x:c r="K41" s="40"/>
       <x:c r="L41" s="40"/>
+      <x:c r="M41"/>
+      <x:c r="N41"/>
+      <x:c r="O41"/>
+      <x:c r="P41"/>
+      <x:c r="Q41"/>
+      <x:c r="R41"/>
+      <x:c r="S41"/>
+      <x:c r="T41"/>
+      <x:c r="U41"/>
     </x:row>
     <x:row r="42" ht="14.5">
       <x:c r="A42" s="40"/>
@@ -2364,8 +2814,17 @@
       <x:c r="K42" s="40" t="str">
         <x:v>30063;30064;30065</x:v>
       </x:c>
-      <x:c r="L42" s="40" t="n">
-        <x:v>620</x:v>
+      <x:c r="L42" s="40">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="S42">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T42">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42">
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="14.5">
@@ -2387,6 +2846,15 @@
       <x:c r="J43" s="40"/>
       <x:c r="K43" s="40"/>
       <x:c r="L43" s="40"/>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
+      <x:c r="P43"/>
+      <x:c r="Q43"/>
+      <x:c r="R43"/>
+      <x:c r="S43"/>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
     </x:row>
     <x:row r="44" ht="14.5">
       <x:c r="A44" s="40"/>
@@ -2407,6 +2875,15 @@
       <x:c r="J44" s="40"/>
       <x:c r="K44" s="40"/>
       <x:c r="L44" s="40"/>
+      <x:c r="M44"/>
+      <x:c r="N44"/>
+      <x:c r="O44"/>
+      <x:c r="P44"/>
+      <x:c r="Q44"/>
+      <x:c r="R44"/>
+      <x:c r="S44"/>
+      <x:c r="T44"/>
+      <x:c r="U44"/>
     </x:row>
     <x:row r="45" ht="14.5">
       <x:c r="A45" s="40"/>
@@ -2427,6 +2904,15 @@
       <x:c r="J45" s="40"/>
       <x:c r="K45" s="40"/>
       <x:c r="L45" s="40"/>
+      <x:c r="M45"/>
+      <x:c r="N45"/>
+      <x:c r="O45"/>
+      <x:c r="P45"/>
+      <x:c r="Q45"/>
+      <x:c r="R45"/>
+      <x:c r="S45"/>
+      <x:c r="T45"/>
+      <x:c r="U45"/>
     </x:row>
     <x:row r="46" ht="14.5">
       <x:c r="A46" s="40"/>
@@ -2447,6 +2933,15 @@
       <x:c r="J46" s="40"/>
       <x:c r="K46" s="40"/>
       <x:c r="L46" s="40"/>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
+      <x:c r="P46"/>
+      <x:c r="Q46"/>
+      <x:c r="R46"/>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46"/>
     </x:row>
     <x:row r="47" ht="14.5">
       <x:c r="A47" s="40"/>
@@ -2467,6 +2962,15 @@
       <x:c r="J47" s="40"/>
       <x:c r="K47" s="40"/>
       <x:c r="L47" s="40"/>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+      <x:c r="P47"/>
+      <x:c r="Q47"/>
+      <x:c r="R47"/>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47"/>
     </x:row>
     <x:row r="48" ht="14.5">
       <x:c r="A48" s="40"/>
@@ -2487,6 +2991,15 @@
       <x:c r="J48" s="40"/>
       <x:c r="K48" s="40"/>
       <x:c r="L48" s="40"/>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48"/>
+      <x:c r="T48"/>
+      <x:c r="U48"/>
     </x:row>
     <x:row r="49" ht="14.5">
       <x:c r="A49" s="40"/>
@@ -2507,6 +3020,15 @@
       <x:c r="J49" s="40"/>
       <x:c r="K49" s="40"/>
       <x:c r="L49" s="40"/>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
     </x:row>
     <x:row r="50" ht="14.5">
       <x:c r="A50" s="40"/>
@@ -2527,6 +3049,15 @@
       <x:c r="J50" s="40"/>
       <x:c r="K50" s="40"/>
       <x:c r="L50" s="40"/>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
+      <x:c r="S50"/>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
     </x:row>
     <x:row r="51" ht="14.5">
       <x:c r="A51" s="40"/>
@@ -2547,6 +3078,15 @@
       <x:c r="J51" s="40"/>
       <x:c r="K51" s="40"/>
       <x:c r="L51" s="40"/>
+      <x:c r="M51"/>
+      <x:c r="N51"/>
+      <x:c r="O51"/>
+      <x:c r="P51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51"/>
+      <x:c r="S51"/>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
     </x:row>
     <x:row r="52" ht="14.5">
       <x:c r="A52" s="40"/>
@@ -2567,6 +3107,15 @@
       <x:c r="J52" s="40"/>
       <x:c r="K52" s="40"/>
       <x:c r="L52" s="40"/>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
+      <x:c r="S52"/>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
     </x:row>
     <x:row r="53" ht="14.5">
       <x:c r="A53" s="40"/>
@@ -2587,6 +3136,15 @@
       <x:c r="J53" s="40"/>
       <x:c r="K53" s="40"/>
       <x:c r="L53" s="40"/>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+      <x:c r="P53"/>
+      <x:c r="Q53"/>
+      <x:c r="R53"/>
+      <x:c r="S53"/>
+      <x:c r="T53"/>
+      <x:c r="U53"/>
     </x:row>
     <x:row r="54" ht="14.5">
       <x:c r="A54" s="40"/>
@@ -2607,6 +3165,15 @@
       <x:c r="J54" s="40"/>
       <x:c r="K54" s="40"/>
       <x:c r="L54" s="40"/>
+      <x:c r="M54"/>
+      <x:c r="N54"/>
+      <x:c r="O54"/>
+      <x:c r="P54"/>
+      <x:c r="Q54"/>
+      <x:c r="R54"/>
+      <x:c r="S54"/>
+      <x:c r="T54"/>
+      <x:c r="U54"/>
     </x:row>
     <x:row r="55" ht="14.5">
       <x:c r="A55" s="40"/>
@@ -2627,6 +3194,15 @@
       <x:c r="J55" s="40"/>
       <x:c r="K55" s="40"/>
       <x:c r="L55" s="40"/>
+      <x:c r="M55"/>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
+      <x:c r="P55"/>
+      <x:c r="Q55"/>
+      <x:c r="R55"/>
+      <x:c r="S55"/>
+      <x:c r="T55"/>
+      <x:c r="U55"/>
     </x:row>
     <x:row r="56" ht="14.5">
       <x:c r="A56" s="40"/>
@@ -2647,6 +3223,15 @@
       <x:c r="J56" s="40"/>
       <x:c r="K56" s="40"/>
       <x:c r="L56" s="40"/>
+      <x:c r="M56"/>
+      <x:c r="N56"/>
+      <x:c r="O56"/>
+      <x:c r="P56"/>
+      <x:c r="Q56"/>
+      <x:c r="R56"/>
+      <x:c r="S56"/>
+      <x:c r="T56"/>
+      <x:c r="U56"/>
     </x:row>
     <x:row r="57" ht="14.5">
       <x:c r="A57" s="40"/>
@@ -2667,6 +3252,15 @@
       <x:c r="J57" s="40"/>
       <x:c r="K57" s="40"/>
       <x:c r="L57" s="40"/>
+      <x:c r="M57"/>
+      <x:c r="N57"/>
+      <x:c r="O57"/>
+      <x:c r="P57"/>
+      <x:c r="Q57"/>
+      <x:c r="R57"/>
+      <x:c r="S57"/>
+      <x:c r="T57"/>
+      <x:c r="U57"/>
     </x:row>
     <x:row r="58" ht="14.5">
       <x:c r="A58" s="40"/>
@@ -2687,6 +3281,15 @@
       <x:c r="J58" s="40"/>
       <x:c r="K58" s="40"/>
       <x:c r="L58" s="40"/>
+      <x:c r="M58"/>
+      <x:c r="N58"/>
+      <x:c r="O58"/>
+      <x:c r="P58"/>
+      <x:c r="Q58"/>
+      <x:c r="R58"/>
+      <x:c r="S58"/>
+      <x:c r="T58"/>
+      <x:c r="U58"/>
     </x:row>
     <x:row r="59" ht="14.5">
       <x:c r="A59" s="40"/>
@@ -2707,6 +3310,15 @@
       <x:c r="J59" s="40"/>
       <x:c r="K59" s="40"/>
       <x:c r="L59" s="40"/>
+      <x:c r="M59"/>
+      <x:c r="N59"/>
+      <x:c r="O59"/>
+      <x:c r="P59"/>
+      <x:c r="Q59"/>
+      <x:c r="R59"/>
+      <x:c r="S59"/>
+      <x:c r="T59"/>
+      <x:c r="U59"/>
     </x:row>
     <x:row r="60" ht="14.5">
       <x:c r="A60" s="40"/>
@@ -2727,6 +3339,15 @@
       <x:c r="J60" s="40"/>
       <x:c r="K60" s="40"/>
       <x:c r="L60" s="40"/>
+      <x:c r="M60"/>
+      <x:c r="N60"/>
+      <x:c r="O60"/>
+      <x:c r="P60"/>
+      <x:c r="Q60"/>
+      <x:c r="R60"/>
+      <x:c r="S60"/>
+      <x:c r="T60"/>
+      <x:c r="U60"/>
     </x:row>
     <x:row r="61" ht="14.5">
       <x:c r="A61" s="40"/>
@@ -2747,6 +3368,15 @@
       <x:c r="J61" s="40"/>
       <x:c r="K61" s="40"/>
       <x:c r="L61" s="40"/>
+      <x:c r="M61"/>
+      <x:c r="N61"/>
+      <x:c r="O61"/>
+      <x:c r="P61"/>
+      <x:c r="Q61"/>
+      <x:c r="R61"/>
+      <x:c r="S61"/>
+      <x:c r="T61"/>
+      <x:c r="U61"/>
     </x:row>
     <x:row r="62" ht="14.5">
       <x:c r="A62" s="40"/>
@@ -2767,6 +3397,15 @@
       <x:c r="J62" s="40"/>
       <x:c r="K62" s="40"/>
       <x:c r="L62" s="40"/>
+      <x:c r="M62"/>
+      <x:c r="N62"/>
+      <x:c r="O62"/>
+      <x:c r="P62"/>
+      <x:c r="Q62"/>
+      <x:c r="R62"/>
+      <x:c r="S62"/>
+      <x:c r="T62"/>
+      <x:c r="U62"/>
     </x:row>
     <x:row r="63" ht="14.5">
       <x:c r="A63" s="40"/>
@@ -2787,6 +3426,15 @@
       <x:c r="J63" s="40"/>
       <x:c r="K63" s="40"/>
       <x:c r="L63" s="40"/>
+      <x:c r="M63"/>
+      <x:c r="N63"/>
+      <x:c r="O63"/>
+      <x:c r="P63"/>
+      <x:c r="Q63"/>
+      <x:c r="R63"/>
+      <x:c r="S63"/>
+      <x:c r="T63"/>
+      <x:c r="U63"/>
     </x:row>
     <x:row r="64" ht="14.5">
       <x:c r="A64" s="40"/>
@@ -2807,6 +3455,15 @@
       <x:c r="J64" s="40"/>
       <x:c r="K64" s="40"/>
       <x:c r="L64" s="40"/>
+      <x:c r="M64"/>
+      <x:c r="N64"/>
+      <x:c r="O64"/>
+      <x:c r="P64"/>
+      <x:c r="Q64"/>
+      <x:c r="R64"/>
+      <x:c r="S64"/>
+      <x:c r="T64"/>
+      <x:c r="U64"/>
     </x:row>
     <x:row r="65" ht="14.5">
       <x:c r="A65" s="40"/>
@@ -2827,6 +3484,15 @@
       <x:c r="J65" s="40"/>
       <x:c r="K65" s="40"/>
       <x:c r="L65" s="40"/>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
+      <x:c r="O65"/>
+      <x:c r="P65"/>
+      <x:c r="Q65"/>
+      <x:c r="R65"/>
+      <x:c r="S65"/>
+      <x:c r="T65"/>
+      <x:c r="U65"/>
     </x:row>
     <x:row r="66" ht="14.5">
       <x:c r="A66" s="40"/>
@@ -2847,6 +3513,15 @@
       <x:c r="J66" s="40"/>
       <x:c r="K66" s="40"/>
       <x:c r="L66" s="40"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+      <x:c r="P66"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
+      <x:c r="S66"/>
+      <x:c r="T66"/>
+      <x:c r="U66"/>
     </x:row>
     <x:row r="67" ht="14.5">
       <x:c r="A67" s="40"/>
@@ -2867,6 +3542,15 @@
       <x:c r="J67" s="40"/>
       <x:c r="K67" s="40"/>
       <x:c r="L67" s="40"/>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
+      <x:c r="P67"/>
+      <x:c r="Q67"/>
+      <x:c r="R67"/>
+      <x:c r="S67"/>
+      <x:c r="T67"/>
+      <x:c r="U67"/>
     </x:row>
     <x:row r="68" ht="14.5">
       <x:c r="A68" s="40"/>
@@ -2887,6 +3571,15 @@
       <x:c r="J68" s="40"/>
       <x:c r="K68" s="40"/>
       <x:c r="L68" s="40"/>
+      <x:c r="M68"/>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
+      <x:c r="P68"/>
+      <x:c r="Q68"/>
+      <x:c r="R68"/>
+      <x:c r="S68"/>
+      <x:c r="T68"/>
+      <x:c r="U68"/>
     </x:row>
     <x:row r="69" ht="14.5">
       <x:c r="A69" s="40"/>
@@ -2907,6 +3600,15 @@
       <x:c r="J69" s="40"/>
       <x:c r="K69" s="40"/>
       <x:c r="L69" s="40"/>
+      <x:c r="M69"/>
+      <x:c r="N69"/>
+      <x:c r="O69"/>
+      <x:c r="P69"/>
+      <x:c r="Q69"/>
+      <x:c r="R69"/>
+      <x:c r="S69"/>
+      <x:c r="T69"/>
+      <x:c r="U69"/>
     </x:row>
     <x:row r="70" ht="14.5">
       <x:c r="A70" s="40"/>
@@ -2927,6 +3629,15 @@
       <x:c r="J70" s="40"/>
       <x:c r="K70" s="40"/>
       <x:c r="L70" s="40"/>
+      <x:c r="M70"/>
+      <x:c r="N70"/>
+      <x:c r="O70"/>
+      <x:c r="P70"/>
+      <x:c r="Q70"/>
+      <x:c r="R70"/>
+      <x:c r="S70"/>
+      <x:c r="T70"/>
+      <x:c r="U70"/>
     </x:row>
     <x:row r="71" ht="14.5">
       <x:c r="A71" s="40"/>
@@ -2947,6 +3658,15 @@
       <x:c r="J71" s="40"/>
       <x:c r="K71" s="40"/>
       <x:c r="L71" s="40"/>
+      <x:c r="M71"/>
+      <x:c r="N71"/>
+      <x:c r="O71"/>
+      <x:c r="P71"/>
+      <x:c r="Q71"/>
+      <x:c r="R71"/>
+      <x:c r="S71"/>
+      <x:c r="T71"/>
+      <x:c r="U71"/>
     </x:row>
     <x:row r="72" ht="14.5">
       <x:c r="A72" s="40"/>
@@ -2967,6 +3687,15 @@
       <x:c r="J72" s="40"/>
       <x:c r="K72" s="40"/>
       <x:c r="L72" s="40"/>
+      <x:c r="M72"/>
+      <x:c r="N72"/>
+      <x:c r="O72"/>
+      <x:c r="P72"/>
+      <x:c r="Q72"/>
+      <x:c r="R72"/>
+      <x:c r="S72"/>
+      <x:c r="T72"/>
+      <x:c r="U72"/>
     </x:row>
     <x:row r="73" ht="14.5">
       <x:c r="A73" s="40"/>
@@ -2987,6 +3716,15 @@
       <x:c r="J73" s="40"/>
       <x:c r="K73" s="40"/>
       <x:c r="L73" s="40"/>
+      <x:c r="M73"/>
+      <x:c r="N73"/>
+      <x:c r="O73"/>
+      <x:c r="P73"/>
+      <x:c r="Q73"/>
+      <x:c r="R73"/>
+      <x:c r="S73"/>
+      <x:c r="T73"/>
+      <x:c r="U73"/>
     </x:row>
     <x:row r="74" ht="14.5">
       <x:c r="A74" s="40"/>
@@ -3007,6 +3745,15 @@
       <x:c r="J74" s="40"/>
       <x:c r="K74" s="40"/>
       <x:c r="L74" s="40"/>
+      <x:c r="M74"/>
+      <x:c r="N74"/>
+      <x:c r="O74"/>
+      <x:c r="P74"/>
+      <x:c r="Q74"/>
+      <x:c r="R74"/>
+      <x:c r="S74"/>
+      <x:c r="T74"/>
+      <x:c r="U74"/>
     </x:row>
     <x:row r="75" ht="14.5">
       <x:c r="A75" s="40"/>
@@ -3027,6 +3774,15 @@
       <x:c r="J75" s="40"/>
       <x:c r="K75" s="40"/>
       <x:c r="L75" s="40"/>
+      <x:c r="M75"/>
+      <x:c r="N75"/>
+      <x:c r="O75"/>
+      <x:c r="P75"/>
+      <x:c r="Q75"/>
+      <x:c r="R75"/>
+      <x:c r="S75"/>
+      <x:c r="T75"/>
+      <x:c r="U75"/>
     </x:row>
     <x:row r="76" ht="14.5">
       <x:c r="A76" s="40"/>
@@ -3047,6 +3803,15 @@
       <x:c r="J76" s="40"/>
       <x:c r="K76" s="40"/>
       <x:c r="L76" s="40"/>
+      <x:c r="M76"/>
+      <x:c r="N76"/>
+      <x:c r="O76"/>
+      <x:c r="P76"/>
+      <x:c r="Q76"/>
+      <x:c r="R76"/>
+      <x:c r="S76"/>
+      <x:c r="T76"/>
+      <x:c r="U76"/>
     </x:row>
     <x:row r="77" ht="14.5">
       <x:c r="A77" s="40"/>
@@ -3067,6 +3832,15 @@
       <x:c r="J77" s="40"/>
       <x:c r="K77" s="40"/>
       <x:c r="L77" s="40"/>
+      <x:c r="M77"/>
+      <x:c r="N77"/>
+      <x:c r="O77"/>
+      <x:c r="P77"/>
+      <x:c r="Q77"/>
+      <x:c r="R77"/>
+      <x:c r="S77"/>
+      <x:c r="T77"/>
+      <x:c r="U77"/>
     </x:row>
     <x:row r="78" ht="14.5">
       <x:c r="A78" s="40"/>
@@ -3087,6 +3861,15 @@
       <x:c r="J78" s="40"/>
       <x:c r="K78" s="40"/>
       <x:c r="L78" s="40"/>
+      <x:c r="M78"/>
+      <x:c r="N78"/>
+      <x:c r="O78"/>
+      <x:c r="P78"/>
+      <x:c r="Q78"/>
+      <x:c r="R78"/>
+      <x:c r="S78"/>
+      <x:c r="T78"/>
+      <x:c r="U78"/>
     </x:row>
     <x:row r="79" ht="14.5">
       <x:c r="A79" s="40"/>
@@ -3107,6 +3890,15 @@
       <x:c r="J79" s="40"/>
       <x:c r="K79" s="40"/>
       <x:c r="L79" s="40"/>
+      <x:c r="M79"/>
+      <x:c r="N79"/>
+      <x:c r="O79"/>
+      <x:c r="P79"/>
+      <x:c r="Q79"/>
+      <x:c r="R79"/>
+      <x:c r="S79"/>
+      <x:c r="T79"/>
+      <x:c r="U79"/>
     </x:row>
     <x:row r="80" ht="14.5">
       <x:c r="A80" s="40"/>
@@ -3127,6 +3919,15 @@
       <x:c r="J80" s="40"/>
       <x:c r="K80" s="40"/>
       <x:c r="L80" s="40"/>
+      <x:c r="M80"/>
+      <x:c r="N80"/>
+      <x:c r="O80"/>
+      <x:c r="P80"/>
+      <x:c r="Q80"/>
+      <x:c r="R80"/>
+      <x:c r="S80"/>
+      <x:c r="T80"/>
+      <x:c r="U80"/>
     </x:row>
     <x:row r="81" ht="14.5">
       <x:c r="A81" s="40"/>
@@ -3147,6 +3948,15 @@
       <x:c r="J81" s="40"/>
       <x:c r="K81" s="40"/>
       <x:c r="L81" s="40"/>
+      <x:c r="M81"/>
+      <x:c r="N81"/>
+      <x:c r="O81"/>
+      <x:c r="P81"/>
+      <x:c r="Q81"/>
+      <x:c r="R81"/>
+      <x:c r="S81"/>
+      <x:c r="T81"/>
+      <x:c r="U81"/>
     </x:row>
     <x:row r="82" ht="14.5">
       <x:c r="A82" s="40"/>
@@ -3167,6 +3977,15 @@
       <x:c r="J82" s="40"/>
       <x:c r="K82" s="40"/>
       <x:c r="L82" s="40"/>
+      <x:c r="M82"/>
+      <x:c r="N82"/>
+      <x:c r="O82"/>
+      <x:c r="P82"/>
+      <x:c r="Q82"/>
+      <x:c r="R82"/>
+      <x:c r="S82"/>
+      <x:c r="T82"/>
+      <x:c r="U82"/>
     </x:row>
     <x:row r="83" ht="14.5">
       <x:c r="A83" s="40"/>
@@ -3187,6 +4006,15 @@
       <x:c r="J83" s="40"/>
       <x:c r="K83" s="40"/>
       <x:c r="L83" s="40"/>
+      <x:c r="M83"/>
+      <x:c r="N83"/>
+      <x:c r="O83"/>
+      <x:c r="P83"/>
+      <x:c r="Q83"/>
+      <x:c r="R83"/>
+      <x:c r="S83"/>
+      <x:c r="T83"/>
+      <x:c r="U83"/>
     </x:row>
     <x:row r="84" ht="14.5">
       <x:c r="A84" s="40"/>
@@ -3207,6 +4035,15 @@
       <x:c r="J84" s="40"/>
       <x:c r="K84" s="40"/>
       <x:c r="L84" s="40"/>
+      <x:c r="M84"/>
+      <x:c r="N84"/>
+      <x:c r="O84"/>
+      <x:c r="P84"/>
+      <x:c r="Q84"/>
+      <x:c r="R84"/>
+      <x:c r="S84"/>
+      <x:c r="T84"/>
+      <x:c r="U84"/>
     </x:row>
     <x:row r="85" ht="14.5">
       <x:c r="A85" s="40"/>
@@ -3227,6 +4064,15 @@
       <x:c r="J85" s="40"/>
       <x:c r="K85" s="40"/>
       <x:c r="L85" s="40"/>
+      <x:c r="M85"/>
+      <x:c r="N85"/>
+      <x:c r="O85"/>
+      <x:c r="P85"/>
+      <x:c r="Q85"/>
+      <x:c r="R85"/>
+      <x:c r="S85"/>
+      <x:c r="T85"/>
+      <x:c r="U85"/>
     </x:row>
     <x:row r="86" ht="14.5">
       <x:c r="A86" s="40"/>
@@ -3247,6 +4093,15 @@
       <x:c r="J86" s="40"/>
       <x:c r="K86" s="40"/>
       <x:c r="L86" s="40"/>
+      <x:c r="M86"/>
+      <x:c r="N86"/>
+      <x:c r="O86"/>
+      <x:c r="P86"/>
+      <x:c r="Q86"/>
+      <x:c r="R86"/>
+      <x:c r="S86"/>
+      <x:c r="T86"/>
+      <x:c r="U86"/>
     </x:row>
     <x:row r="87" ht="14.5">
       <x:c r="A87" s="40"/>
@@ -3267,6 +4122,15 @@
       <x:c r="J87" s="40"/>
       <x:c r="K87" s="40"/>
       <x:c r="L87" s="40"/>
+      <x:c r="M87"/>
+      <x:c r="N87"/>
+      <x:c r="O87"/>
+      <x:c r="P87"/>
+      <x:c r="Q87"/>
+      <x:c r="R87"/>
+      <x:c r="S87"/>
+      <x:c r="T87"/>
+      <x:c r="U87"/>
     </x:row>
     <x:row r="88" ht="14.5">
       <x:c r="A88" s="40"/>
@@ -3287,6 +4151,15 @@
       <x:c r="J88" s="40"/>
       <x:c r="K88" s="40"/>
       <x:c r="L88" s="40"/>
+      <x:c r="M88"/>
+      <x:c r="N88"/>
+      <x:c r="O88"/>
+      <x:c r="P88"/>
+      <x:c r="Q88"/>
+      <x:c r="R88"/>
+      <x:c r="S88"/>
+      <x:c r="T88"/>
+      <x:c r="U88"/>
     </x:row>
     <x:row r="89" ht="14.5">
       <x:c r="A89" s="40"/>
@@ -3307,6 +4180,15 @@
       <x:c r="J89" s="40"/>
       <x:c r="K89" s="40"/>
       <x:c r="L89" s="40"/>
+      <x:c r="M89"/>
+      <x:c r="N89"/>
+      <x:c r="O89"/>
+      <x:c r="P89"/>
+      <x:c r="Q89"/>
+      <x:c r="R89"/>
+      <x:c r="S89"/>
+      <x:c r="T89"/>
+      <x:c r="U89"/>
     </x:row>
     <x:row r="90" ht="14.5">
       <x:c r="A90" s="40"/>
@@ -3327,6 +4209,15 @@
       <x:c r="J90" s="40"/>
       <x:c r="K90" s="40"/>
       <x:c r="L90" s="40"/>
+      <x:c r="M90"/>
+      <x:c r="N90"/>
+      <x:c r="O90"/>
+      <x:c r="P90"/>
+      <x:c r="Q90"/>
+      <x:c r="R90"/>
+      <x:c r="S90"/>
+      <x:c r="T90"/>
+      <x:c r="U90"/>
     </x:row>
     <x:row r="91" ht="14.5">
       <x:c r="A91" s="40"/>
@@ -3347,6 +4238,15 @@
       <x:c r="J91" s="40"/>
       <x:c r="K91" s="40"/>
       <x:c r="L91" s="40"/>
+      <x:c r="M91"/>
+      <x:c r="N91"/>
+      <x:c r="O91"/>
+      <x:c r="P91"/>
+      <x:c r="Q91"/>
+      <x:c r="R91"/>
+      <x:c r="S91"/>
+      <x:c r="T91"/>
+      <x:c r="U91"/>
     </x:row>
     <x:row r="92" ht="14.5">
       <x:c r="A92" s="40"/>
@@ -3367,6 +4267,15 @@
       <x:c r="J92" s="40"/>
       <x:c r="K92" s="40"/>
       <x:c r="L92" s="40"/>
+      <x:c r="M92"/>
+      <x:c r="N92"/>
+      <x:c r="O92"/>
+      <x:c r="P92"/>
+      <x:c r="Q92"/>
+      <x:c r="R92"/>
+      <x:c r="S92"/>
+      <x:c r="T92"/>
+      <x:c r="U92"/>
     </x:row>
     <x:row r="93" ht="14.5">
       <x:c r="A93" s="40"/>
@@ -3387,6 +4296,15 @@
       <x:c r="J93" s="40"/>
       <x:c r="K93" s="40"/>
       <x:c r="L93" s="40"/>
+      <x:c r="M93"/>
+      <x:c r="N93"/>
+      <x:c r="O93"/>
+      <x:c r="P93"/>
+      <x:c r="Q93"/>
+      <x:c r="R93"/>
+      <x:c r="S93"/>
+      <x:c r="T93"/>
+      <x:c r="U93"/>
     </x:row>
     <x:row r="94" ht="14.5">
       <x:c r="A94" s="40"/>
@@ -3407,6 +4325,15 @@
       <x:c r="J94" s="40"/>
       <x:c r="K94" s="40"/>
       <x:c r="L94" s="40"/>
+      <x:c r="M94"/>
+      <x:c r="N94"/>
+      <x:c r="O94"/>
+      <x:c r="P94"/>
+      <x:c r="Q94"/>
+      <x:c r="R94"/>
+      <x:c r="S94"/>
+      <x:c r="T94"/>
+      <x:c r="U94"/>
     </x:row>
     <x:row r="95" ht="14.5">
       <x:c r="A95" s="40"/>
@@ -3427,6 +4354,15 @@
       <x:c r="J95" s="40"/>
       <x:c r="K95" s="40"/>
       <x:c r="L95" s="40"/>
+      <x:c r="M95"/>
+      <x:c r="N95"/>
+      <x:c r="O95"/>
+      <x:c r="P95"/>
+      <x:c r="Q95"/>
+      <x:c r="R95"/>
+      <x:c r="S95"/>
+      <x:c r="T95"/>
+      <x:c r="U95"/>
     </x:row>
     <x:row r="96" ht="14.5">
       <x:c r="A96" s="40"/>
@@ -3447,6 +4383,15 @@
       <x:c r="J96" s="40"/>
       <x:c r="K96" s="40"/>
       <x:c r="L96" s="40"/>
+      <x:c r="M96"/>
+      <x:c r="N96"/>
+      <x:c r="O96"/>
+      <x:c r="P96"/>
+      <x:c r="Q96"/>
+      <x:c r="R96"/>
+      <x:c r="S96"/>
+      <x:c r="T96"/>
+      <x:c r="U96"/>
     </x:row>
     <x:row r="97" ht="14.5">
       <x:c r="A97" s="40"/>
@@ -3467,6 +4412,15 @@
       <x:c r="J97" s="40"/>
       <x:c r="K97" s="40"/>
       <x:c r="L97" s="40"/>
+      <x:c r="M97"/>
+      <x:c r="N97"/>
+      <x:c r="O97"/>
+      <x:c r="P97"/>
+      <x:c r="Q97"/>
+      <x:c r="R97"/>
+      <x:c r="S97"/>
+      <x:c r="T97"/>
+      <x:c r="U97"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="Rb2629634b2cf48d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R9a919821b74947a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1445,13 +1445,13 @@
         <x:v>combatProfileId</x:v>
       </x:c>
       <x:c r="F1" s="50" t="str">
-        <x:v>projectileRadiusPixelsMilli</x:v>
+        <x:v>projectileRadiusPixels</x:v>
       </x:c>
       <x:c r="G1" s="50" t="str">
-        <x:v>projectileOffsetXPixelsMilli</x:v>
+        <x:v>projectileOffsetXPixels</x:v>
       </x:c>
       <x:c r="H1" s="50" t="str">
-        <x:v>projectileOffsetYPixelsMilli</x:v>
+        <x:v>projectileOffsetYPixels</x:v>
       </x:c>
       <x:c r="I1" s="50" t="str">
         <x:v>projectileClipId</x:v>
@@ -1463,31 +1463,31 @@
         <x:v>areaClipIds</x:v>
       </x:c>
       <x:c r="L1" s="50" t="str">
-        <x:v>areaRadiusPixelsMilli</x:v>
+        <x:v>areaRadiusPixels</x:v>
       </x:c>
       <x:c r="M1" t="str">
-        <x:v>projectileVisualOffsetXPixelsMilli</x:v>
+        <x:v>projectileVisualOffsetXPixels</x:v>
       </x:c>
       <x:c r="N1" t="str">
-        <x:v>projectileVisualOffsetYPixelsMilli</x:v>
+        <x:v>projectileVisualOffsetYPixels</x:v>
       </x:c>
       <x:c r="O1" t="str">
         <x:v>projectileVisualScalePermille</x:v>
       </x:c>
       <x:c r="P1" t="str">
-        <x:v>impactVisualOffsetXPixelsMilli</x:v>
+        <x:v>impactVisualOffsetXPixels</x:v>
       </x:c>
       <x:c r="Q1" t="str">
-        <x:v>impactVisualOffsetYPixelsMilli</x:v>
+        <x:v>impactVisualOffsetYPixels</x:v>
       </x:c>
       <x:c r="R1" t="str">
         <x:v>impactVisualScalePermille</x:v>
       </x:c>
       <x:c r="S1" t="str">
-        <x:v>areaVisualOffsetXPixelsMilli</x:v>
+        <x:v>areaVisualOffsetXPixels</x:v>
       </x:c>
       <x:c r="T1" t="str">
-        <x:v>areaVisualOffsetYPixelsMilli</x:v>
+        <x:v>areaVisualOffsetYPixels</x:v>
       </x:c>
       <x:c r="U1" t="str">
         <x:v>areaVisualScalePermille</x:v>
@@ -1510,13 +1510,13 @@
         <x:v>int?#ref=TbSkillCombat</x:v>
       </x:c>
       <x:c r="F2" s="53" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="G2" s="53" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="H2" s="53" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="I2" s="53" t="str">
         <x:v>int?#ref=TbAnimationClip</x:v>
@@ -1528,31 +1528,31 @@
         <x:v>(list#sep=;),int#ref=TbAnimationClip</x:v>
       </x:c>
       <x:c r="L2" s="53" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="O2" t="str">
         <x:v>int?</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="R2" t="str">
         <x:v>int?</x:v>
       </x:c>
       <x:c r="S2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="T2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="U2" t="str">
         <x:v>int?</x:v>
@@ -1600,13 +1600,13 @@
         <x:v>战斗机制；空值仅为表现目录</x:v>
       </x:c>
       <x:c r="F4" s="62" t="str">
-        <x:v>弹丸命中半径（像素）；由技能预制体“弹丸命中范围”节点导出；非弹丸留空。</x:v>
+        <x:v>弹丸命中半径；由技能预制体“弹丸命中范围”节点导出；非弹丸留空，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="G4" s="62" t="str">
-        <x:v>弹丸命中中心横向偏移（像素）；技能局部右向；由技能预制体导出。</x:v>
+        <x:v>弹丸命中中心横向偏移；技能局部右向；由技能预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="H4" s="62" t="str">
-        <x:v>弹丸命中中心前向偏移（像素）；由技能预制体导出。</x:v>
+        <x:v>弹丸命中中心前向偏移；由技能预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="I4" s="62" t="str">
         <x:v>弹丸飞行表现；Projectile必填</x:v>
@@ -1618,31 +1618,31 @@
         <x:v>TargetArea在目标位置叠加播放的片段</x:v>
       </x:c>
       <x:c r="L4" s="62" t="str">
-        <x:v>范围技能命中半径（像素）；由技能预制体“范围技能命中范围”节点导出；非范围技能留空。</x:v>
+        <x:v>范围技能命中半径；由技能预制体“范围技能命中范围”节点导出；非范围技能留空，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>弹丸表现横向偏移（逻辑像素）；由技能预制体“弹丸表现”节点导出。</x:v>
+        <x:v>弹丸表现横向偏移；由技能预制体“弹丸表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>弹丸表现纵向偏移（逻辑像素）；由技能预制体“弹丸表现”节点导出。</x:v>
+        <x:v>弹丸表现纵向偏移；由技能预制体“弹丸表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="O4" t="str">
         <x:v>弹丸表现相对缩放（千分比）；由技能预制体“弹丸表现”节点统一 Scale 导出。</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>命中特效表现横向偏移（逻辑像素）；由技能预制体“命中特效表现”节点导出。</x:v>
+        <x:v>命中特效表现横向偏移；由技能预制体“命中特效表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>命中特效表现纵向偏移（逻辑像素）；由技能预制体“命中特效表现”节点导出。</x:v>
+        <x:v>命中特效表现纵向偏移；由技能预制体“命中特效表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="R4" t="str">
         <x:v>命中特效表现相对缩放（千分比）；由技能预制体“命中特效表现”节点统一 Scale 导出。</x:v>
       </x:c>
       <x:c r="S4" t="str">
-        <x:v>范围特效表现横向偏移（逻辑像素）；由技能预制体“范围特效表现”节点导出。</x:v>
+        <x:v>范围特效表现横向偏移；由技能预制体“范围特效表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="T4" t="str">
-        <x:v>范围特效表现纵向偏移（逻辑像素）；由技能预制体“范围特效表现”节点导出。</x:v>
+        <x:v>范围特效表现纵向偏移；由技能预制体“范围特效表现”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="U4" t="str">
         <x:v>范围特效表现相对缩放（千分比）；由技能预制体“范围特效表现”节点统一 Scale 导出。</x:v>
@@ -1662,14 +1662,14 @@
       <x:c r="E5" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="40">
-        <x:v>30693</x:v>
-      </x:c>
-      <x:c r="G5" s="40">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="H5" s="40">
-        <x:v>-25000</x:v>
+      <x:c r="F5" s="40" t="n">
+        <x:v>30.693</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="n">
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I5" s="40" t="n">
         <x:v>30002</x:v>
@@ -1679,19 +1679,19 @@
       </x:c>
       <x:c r="K5" s="40"/>
       <x:c r="L5" s="40"/>
-      <x:c r="M5">
+      <x:c r="M5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N5">
+      <x:c r="N5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="P5">
+      <x:c r="P5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q5">
+      <x:c r="Q5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5">
@@ -2004,13 +2004,13 @@
       <x:c r="E16" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" s="40">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="G16" s="40">
+      <x:c r="F16" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="40" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="40">
+      <x:c r="H16" s="40" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="40" t="n">
@@ -2021,19 +2021,19 @@
       </x:c>
       <x:c r="K16" s="40"/>
       <x:c r="L16" s="40"/>
-      <x:c r="M16">
+      <x:c r="M16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N16">
+      <x:c r="N16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="P16">
+      <x:c r="P16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q16">
+      <x:c r="Q16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R16">
@@ -2439,13 +2439,13 @@
       <x:c r="K30" s="40" t="str">
         <x:v>30045</x:v>
       </x:c>
-      <x:c r="L30" s="40">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="S30">
+      <x:c r="L30" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="S30" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="T30">
+      <x:c r="T30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U30">
@@ -2553,13 +2553,13 @@
       <x:c r="E34" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F34" s="40">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="G34" s="40">
+      <x:c r="F34" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G34" s="40" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="40">
+      <x:c r="H34" s="40" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="40" t="n">
@@ -2570,19 +2570,19 @@
       </x:c>
       <x:c r="K34" s="40"/>
       <x:c r="L34" s="40"/>
-      <x:c r="M34">
+      <x:c r="M34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N34">
+      <x:c r="N34" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O34">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="P34">
+      <x:c r="P34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q34">
+      <x:c r="Q34" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R34">
@@ -2814,13 +2814,13 @@
       <x:c r="K42" s="40" t="str">
         <x:v>30063;30064;30065</x:v>
       </x:c>
-      <x:c r="L42" s="40">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="S42">
+      <x:c r="L42" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="S42" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="T42">
+      <x:c r="T42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U42">
